--- a/data/gravel/Bombtrack Hook EXT C 2025.xlsx
+++ b/data/gravel/Bombtrack Hook EXT C 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4207EBF6-89FC-BA48-8440-F015C3192E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764FE060-435E-4745-873E-AA8B8D652045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="1120" windowWidth="26300" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,9 +194,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>steel</t>
-  </si>
-  <si>
     <t>udh</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
   </si>
   <si>
     <t>a8:e32</t>
+  </si>
+  <si>
+    <t>carbon</t>
   </si>
 </sst>
 </file>
@@ -703,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -743,7 +743,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
         <v>39</v>
@@ -1129,7 +1129,7 @@
         <v>1790</v>
       </c>
       <c r="H33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -1149,57 +1149,57 @@
         <v>1880</v>
       </c>
       <c r="H34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" t="s">
         <v>91</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>52</v>
       </c>
-      <c r="B38" t="s">
-        <v>53</v>
+      <c r="B38" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41">
         <v>45</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42">
         <v>57</v>
@@ -1216,27 +1216,27 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47">
         <v>142</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>100</v>
@@ -1252,20 +1252,20 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51">
         <v>27.2</v>
@@ -1273,15 +1273,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53">
         <v>42</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54">
         <v>48</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55">
         <v>180</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56">
         <v>180</v>
@@ -1313,38 +1313,38 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="1">
         <v>1</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B65" s="1">
         <v>3</v>
@@ -1376,46 +1376,46 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Bombtrack Hook EXT C 2025.xlsx
+++ b/data/gravel/Bombtrack Hook EXT C 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764FE060-435E-4745-873E-AA8B8D652045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B8752C-33B5-D643-925C-773351E68505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="1120" windowWidth="26300" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>carbon</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/60d2d479d2b7b75136ea090c/1752675964106-COW7XUO9LAYALS1ZJJJA/Bombtrack_Hook_EXT_C_Apex_AXS_glossy_red_4055822540872_web_1.jpg?format=2500w</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Bombtrack Hook EXT C 2025.xlsx
+++ b/data/gravel/Bombtrack Hook EXT C 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B8752C-33B5-D643-925C-773351E68505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A30DED0-6CDB-EF4B-8B14-C29F8DACD10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="1120" windowWidth="26300" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/60d2d479d2b7b75136ea090c/1752675964106-COW7XUO9LAYALS1ZJJJA/Bombtrack_Hook_EXT_C_Apex_AXS_glossy_red_4055822540872_web_1.jpg?format=2500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Cologne, Germany</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1426,6 +1432,14 @@
         <v>86</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Bombtrack Hook EXT C 2025.xlsx
+++ b/data/gravel/Bombtrack Hook EXT C 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A30DED0-6CDB-EF4B-8B14-C29F8DACD10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304C7154-A88F-AE4A-9AD4-73E92E94B1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2500" yWindow="1120" windowWidth="26300" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>Cologne, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -693,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1266,177 +1284,207 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53">
-        <v>42</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55">
-        <v>180</v>
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56">
-        <v>180</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>68</v>
+      </c>
+      <c r="B60">
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B61">
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>105</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>106</v>
       </c>
     </row>
